--- a/templates/Directory-5.xlsx
+++ b/templates/Directory-5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joseph\Downloads\_sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C11E9D74-C90B-4400-BB46-1491179F820F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B42D19F6-35B2-4BFA-B55A-5B2A76665BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Directory of Participants" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="60">
   <si>
     <t>Directory of Participants</t>
   </si>
@@ -125,13 +125,7 @@
     <t> PREPARED BY:</t>
   </si>
   <si>
-    <t>Training Assistant</t>
-  </si>
-  <si>
     <t>NOTED BY:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Traiing Manager </t>
   </si>
   <si>
     <t>LIST OF TRAININGS CONDUCTED</t>
@@ -215,16 +209,10 @@
     <t>PETROSPHERE INCORPORATED</t>
   </si>
   <si>
-    <t>MICHELLE M. SACLET</t>
+    <t>Training Facilitator</t>
   </si>
   <si>
-    <t>JEFFREY C. GEALON</t>
-  </si>
-  <si>
-    <t>Michelle M. Saclet</t>
-  </si>
-  <si>
-    <t>August 25, 2021</t>
+    <t>Operations Manager</t>
   </si>
 </sst>
 </file>
@@ -1337,7 +1325,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="70" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D9" s="71"/>
       <c r="E9" s="71"/>
@@ -1740,14 +1728,12 @@
       <c r="B29" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="56" t="s">
-        <v>60</v>
-      </c>
+      <c r="C29" s="56"/>
     </row>
     <row r="30" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="52"/>
       <c r="C30" s="41" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1756,15 +1742,13 @@
     </row>
     <row r="32" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" s="51" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="56" t="s">
-        <v>61</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C32" s="56"/>
     </row>
     <row r="33" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C33" s="41" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2759,7 +2743,7 @@
   <sheetData>
     <row r="1" spans="1:13" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="85" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B1" s="85"/>
       <c r="C1" s="85"/>
@@ -2806,7 +2790,7 @@
     </row>
     <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="89" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B4" s="90"/>
       <c r="C4" s="90"/>
@@ -2854,7 +2838,7 @@
     <row r="7" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="40" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C8" s="91" t="s">
         <v>2</v>
@@ -2872,11 +2856,9 @@
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="91" t="s">
-        <v>62</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="C9" s="91"/>
       <c r="D9" s="91"/>
       <c r="E9" s="91"/>
       <c r="F9" s="91"/>
@@ -2890,11 +2872,9 @@
     </row>
     <row r="10" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="92" t="s">
-        <v>63</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="C10" s="92"/>
       <c r="D10" s="92"/>
       <c r="E10" s="92"/>
       <c r="F10" s="92"/>
@@ -2920,28 +2900,28 @@
         <v>6</v>
       </c>
       <c r="B12" s="86" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="86" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="86" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="86" t="s">
+      <c r="E12" s="88" t="s">
         <v>38</v>
-      </c>
-      <c r="D12" s="86" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" s="88" t="s">
-        <v>40</v>
       </c>
       <c r="F12" s="87"/>
       <c r="G12" s="87"/>
       <c r="H12" s="87"/>
       <c r="I12" s="86" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J12" s="87"/>
       <c r="K12" s="87"/>
       <c r="L12" s="87"/>
       <c r="M12" s="88" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:13" s="31" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2950,10 +2930,10 @@
       <c r="C13" s="87"/>
       <c r="D13" s="87"/>
       <c r="E13" s="32" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F13" s="32" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G13" s="33" t="s">
         <v>27</v>
@@ -2962,16 +2942,16 @@
         <v>14</v>
       </c>
       <c r="I13" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="J13" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="K13" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="J13" s="33" t="s">
+      <c r="L13" s="33" t="s">
         <v>46</v>
-      </c>
-      <c r="K13" s="33" t="s">
-        <v>47</v>
-      </c>
-      <c r="L13" s="33" t="s">
-        <v>48</v>
       </c>
       <c r="M13" s="87"/>
     </row>
@@ -4804,7 +4784,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="93" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B1" s="90"/>
       <c r="C1" s="90"/>
@@ -4863,7 +4843,7 @@
     </row>
     <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C5" s="94"/>
       <c r="D5" s="95"/>
@@ -4871,7 +4851,7 @@
     </row>
     <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C6" s="94"/>
       <c r="D6" s="95"/>
@@ -4879,7 +4859,7 @@
     </row>
     <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C7" s="94"/>
       <c r="D7" s="95"/>
@@ -4891,16 +4871,16 @@
         <v>6</v>
       </c>
       <c r="B9" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>39</v>
-      </c>
       <c r="D9" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>10</v>
@@ -4909,31 +4889,31 @@
         <v>12</v>
       </c>
       <c r="H9" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="I9" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>54</v>
-      </c>
       <c r="K9" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="L9" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>48</v>
       </c>
       <c r="M9" s="6" t="s">
         <v>21</v>
       </c>
       <c r="N9" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="P9" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="O9" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="P9" s="7" t="s">
-        <v>57</v>
       </c>
       <c r="Q9" s="8"/>
       <c r="R9" s="8"/>
